--- a/data/trans_orig/P16A04-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A04-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17158</t>
+          <t>18424</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14061</t>
+          <t>13941</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10057</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25671</t>
+          <t>26674</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>476906</t>
+          <t>475640</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>489973</t>
+          <t>489997</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>453428</t>
+          <t>453548</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>463903</t>
+          <t>464412</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>935882</t>
+          <t>934879</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>951496</t>
+          <t>952127</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>14065</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9588</t>
+          <t>9738</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25555</t>
+          <t>25234</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14704</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33277</t>
+          <t>34072</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>721869</t>
+          <t>721424</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>732589</t>
+          <t>732547</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>599939</t>
+          <t>600260</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>615906</t>
+          <t>615756</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1327705</t>
+          <t>1326910</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1346278</t>
+          <t>1345398</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10889</t>
+          <t>11126</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>7840</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24616</t>
+          <t>24223</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12004</t>
+          <t>11073</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30248</t>
+          <t>28930</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>626760</t>
+          <t>626523</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>635784</t>
+          <t>635777</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>665128</t>
+          <t>665521</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>682005</t>
+          <t>681904</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1297146</t>
+          <t>1298464</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1315390</t>
+          <t>1316321</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17206</t>
+          <t>16115</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13859</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9769</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26758</t>
+          <t>24308</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>501941</t>
+          <t>503032</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>515415</t>
+          <t>515364</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>501783</t>
+          <t>501761</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>512615</t>
+          <t>512596</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1008031</t>
+          <t>1010481</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1025020</t>
+          <t>1026125</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6911</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21656</t>
+          <t>22150</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4244</t>
+          <t>4384</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16812</t>
+          <t>16708</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14044</t>
+          <t>13944</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32684</t>
+          <t>32215</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>365054</t>
+          <t>364560</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>379799</t>
+          <t>379419</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>387174</t>
+          <t>387278</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>399742</t>
+          <t>399602</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>758012</t>
+          <t>758481</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>776652</t>
+          <t>776752</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4612</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15722</t>
+          <t>15640</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,44 +2463,44 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>5,35%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>9901</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>5426</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>16616</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
           <t>1,58%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>9901</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>5063</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>16636</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
           <t>4,85%</t>
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12067</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28254</t>
+          <t>28188</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276861</t>
+          <t>276943</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287971</t>
+          <t>288016</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,49 +2576,49 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>98,44%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>333033</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>326318</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>337508</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>97,11%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>95,15%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
           <t>98,42%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>333033</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>326298</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>337871</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>97,11%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>95,15%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>98,52%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>653</t>
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>607263</t>
+          <t>607329</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>623450</t>
+          <t>623490</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15001</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20144</t>
+          <t>19527</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11103</t>
+          <t>11245</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29349</t>
+          <t>29447</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>194882</t>
+          <t>194078</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>206278</t>
+          <t>206288</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>313764</t>
+          <t>314381</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>328386</t>
+          <t>328691</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>514442</t>
+          <t>514344</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>532688</t>
+          <t>532546</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>45782</t>
+          <t>45311</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>74568</t>
+          <t>75059</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58066</t>
+          <t>59272</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>93580</t>
+          <t>93543</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>112047</t>
+          <t>112191</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>158487</t>
+          <t>155307</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3200957</t>
+          <t>3200466</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3229743</t>
+          <t>3230214</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3285617</t>
+          <t>3285654</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3321131</t>
+          <t>3319925</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6496235</t>
+          <t>6499415</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6542675</t>
+          <t>6542531</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17347</t>
+          <t>16890</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>8992</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>23934</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16319</t>
+          <t>16419</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35356</t>
+          <t>35965</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>435758</t>
+          <t>436215</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>448495</t>
+          <t>449134</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>405873</t>
+          <t>405405</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>420453</t>
+          <t>420347</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>847089</t>
+          <t>846480</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>866126</t>
+          <t>866026</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10978</t>
+          <t>12145</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29452</t>
+          <t>30842</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>17755</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41373</t>
+          <t>39821</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33554</t>
+          <t>33193</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62097</t>
+          <t>63245</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>656786</t>
+          <t>655396</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>675260</t>
+          <t>674093</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>568882</t>
+          <t>570434</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>592114</t>
+          <t>592500</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1234396</t>
+          <t>1233248</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1262939</t>
+          <t>1263300</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9286</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24992</t>
+          <t>25210</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10745</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27519</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23477</t>
+          <t>22817</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47617</t>
+          <t>46457</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>654168</t>
+          <t>653950</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>669874</t>
+          <t>670451</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>677418</t>
+          <t>675097</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>694262</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1336480</t>
+          <t>1337640</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1360620</t>
+          <t>1361280</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22183</t>
+          <t>21285</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17693</t>
+          <t>18828</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12823</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33567</t>
+          <t>33243</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>592434</t>
+          <t>593332</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>608119</t>
+          <t>608321</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>596379</t>
+          <t>595244</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>609678</t>
+          <t>608825</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1195122</t>
+          <t>1195446</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1215866</t>
+          <t>1215373</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21375</t>
+          <t>23010</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16063</t>
+          <t>16467</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12983</t>
+          <t>13541</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34259</t>
+          <t>33240</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>406969</t>
+          <t>405334</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>421436</t>
+          <t>421534</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>431737</t>
+          <t>431333</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>443657</t>
+          <t>443682</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>841885</t>
+          <t>842904</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>863161</t>
+          <t>862603</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9098</t>
+          <t>9386</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31123</t>
+          <t>31815</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16613</t>
+          <t>17729</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16976</t>
+          <t>16640</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41611</t>
+          <t>41738</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276672</t>
+          <t>275980</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>298697</t>
+          <t>298409</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>336446</t>
+          <t>335330</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>348469</t>
+          <t>348362</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>619243</t>
+          <t>619116</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>643878</t>
+          <t>644214</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19651</t>
+          <t>18125</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>6981</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22249</t>
+          <t>21517</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14439</t>
+          <t>14151</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36170</t>
+          <t>33846</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>227193</t>
+          <t>228719</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>242358</t>
+          <t>242375</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>364504</t>
+          <t>365236</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>379111</t>
+          <t>379772</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>597427</t>
+          <t>599751</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>619158</t>
+          <t>619446</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73191</t>
+          <t>76700</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>118752</t>
+          <t>118937</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>83466</t>
+          <t>80717</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>124986</t>
+          <t>122792</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>168636</t>
+          <t>168871</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>229140</t>
+          <t>228183</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3297351</t>
+          <t>3297166</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3342912</t>
+          <t>3339403</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3421231</t>
+          <t>3423425</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3462751</t>
+          <t>3465500</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6733180</t>
+          <t>6734137</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6793684</t>
+          <t>6793449</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>924</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17790</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6747</t>
+          <t>7511</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20443</t>
+          <t>20512</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>412475</t>
+          <t>411885</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>418544</t>
+          <t>418539</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>377965</t>
+          <t>378309</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>390849</t>
+          <t>390892</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>794775</t>
+          <t>794706</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>808471</t>
+          <t>807707</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11482</t>
+          <t>11841</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28509</t>
+          <t>28913</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23093</t>
+          <t>22672</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23163</t>
+          <t>23788</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46181</t>
+          <t>45447</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>561987</t>
+          <t>561583</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>579014</t>
+          <t>578655</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>540451</t>
+          <t>540872</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>555309</t>
+          <t>555201</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1107859</t>
+          <t>1108593</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1130877</t>
+          <t>1130252</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8215</t>
+          <t>8985</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24342</t>
+          <t>25427</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>8489</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24229</t>
+          <t>24514</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18960</t>
+          <t>19271</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40827</t>
+          <t>41038</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>644755</t>
+          <t>643670</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>660882</t>
+          <t>660112</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>637157</t>
+          <t>636872</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>653207</t>
+          <t>652897</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1289656</t>
+          <t>1289445</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1311523</t>
+          <t>1311212</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21547</t>
+          <t>20660</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>10295</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28195</t>
+          <t>28305</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>624501</t>
+          <t>625388</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>639685</t>
+          <t>639762</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>637515</t>
+          <t>637438</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>647120</t>
+          <t>647837</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1266930</t>
+          <t>1266820</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1285213</t>
+          <t>1284830</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18435</t>
+          <t>18362</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10049</t>
+          <t>9860</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28203</t>
+          <t>27693</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17844</t>
+          <t>17605</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39159</t>
+          <t>39018</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>459483</t>
+          <t>459556</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>473162</t>
+          <t>473422</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>468646</t>
+          <t>469156</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>486800</t>
+          <t>486989</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>935608</t>
+          <t>935749</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>956923</t>
+          <t>957162</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17704</t>
+          <t>18459</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4351</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>18295</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10423</t>
+          <t>10087</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30696</t>
+          <t>28743</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>316626</t>
+          <t>315871</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>330111</t>
+          <t>330453</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>360014</t>
+          <t>359467</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>373411</t>
+          <t>374003</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>681396</t>
+          <t>683349</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>701669</t>
+          <t>702005</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19323</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21996</t>
+          <t>22671</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>252008</t>
+          <t>251195</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>380846</t>
+          <t>380925</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>395135</t>
+          <t>395178</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>635171</t>
+          <t>634496</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>651102</t>
+          <t>650773</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53948</t>
+          <t>53214</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>87983</t>
+          <t>86710</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>63427</t>
+          <t>63836</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>102289</t>
+          <t>101231</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>124314</t>
+          <t>126017</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>177422</t>
+          <t>177249</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3306367</t>
+          <t>3307640</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3340402</t>
+          <t>3341136</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3442253</t>
+          <t>3443311</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3481115</t>
+          <t>3480706</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6761470</t>
+          <t>6761643</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6814578</t>
+          <t>6812875</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21991</t>
+          <t>21421</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16296</t>
+          <t>17260</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6954</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33566</t>
+          <t>30805</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>377996</t>
+          <t>378566</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>397853</t>
+          <t>397857</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296904</t>
+          <t>295940</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311001</t>
+          <t>311028</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>679621</t>
+          <t>682382</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>706233</t>
+          <t>706758</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>267</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12953</t>
+          <t>15120</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19524</t>
+          <t>19813</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7415</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26126</t>
+          <t>25992</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>410594</t>
+          <t>408427</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423379</t>
+          <t>423280</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>491980</t>
+          <t>491691</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>506149</t>
+          <t>506589</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>908925</t>
+          <t>909059</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>927636</t>
+          <t>927067</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7356</t>
+          <t>6724</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22109</t>
+          <t>22366</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9835</t>
+          <t>9745</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23171</t>
+          <t>22684</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19250</t>
+          <t>19955</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38893</t>
+          <t>39691</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>514229</t>
+          <t>513972</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>528982</t>
+          <t>529614</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>519297</t>
+          <t>519784</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>532633</t>
+          <t>532723</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1039913</t>
+          <t>1039115</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1059556</t>
+          <t>1058851</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7992</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32245</t>
+          <t>31889</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>15964</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43306</t>
+          <t>42614</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24863</t>
+          <t>26265</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63309</t>
+          <t>66641</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>855541</t>
+          <t>855897</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>879794</t>
+          <t>880477</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>669575</t>
+          <t>670267</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>697028</t>
+          <t>696917</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1537358</t>
+          <t>1534026</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1575804</t>
+          <t>1574402</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8125</t>
+          <t>8406</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23360</t>
+          <t>22023</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15228</t>
+          <t>15158</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28700</t>
+          <t>28268</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26743</t>
+          <t>26586</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45687</t>
+          <t>46388</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>536877</t>
+          <t>538214</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>552112</t>
+          <t>551831</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>516187</t>
+          <t>516619</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>529659</t>
+          <t>529729</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1059437</t>
+          <t>1058736</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1078381</t>
+          <t>1078538</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14932</t>
+          <t>15763</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23057</t>
+          <t>23421</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11303</t>
+          <t>11888</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33490</t>
+          <t>34269</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>353233</t>
+          <t>352402</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>362444</t>
+          <t>362970</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>585311</t>
+          <t>584947</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>603491</t>
+          <t>604512</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>943043</t>
+          <t>942264</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>965230</t>
+          <t>964645</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13848</t>
+          <t>14215</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13031</t>
+          <t>13062</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27070</t>
+          <t>27245</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19328</t>
+          <t>19649</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35542</t>
+          <t>35554</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>268421</t>
+          <t>268054</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>277742</t>
+          <t>277479</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>397324</t>
+          <t>397149</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>411363</t>
+          <t>411332</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>671121</t>
+          <t>671109</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>687335</t>
+          <t>687014</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>56889</t>
+          <t>54005</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>97638</t>
+          <t>97118</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>88403</t>
+          <t>91030</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>136558</t>
+          <t>136067</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>157336</t>
+          <t>154438</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>219395</t>
+          <t>216564</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3360692</t>
+          <t>3361212</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3401441</t>
+          <t>3404325</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3521144</t>
+          <t>3521635</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3569299</t>
+          <t>3566672</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6896637</t>
+          <t>6899468</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6958696</t>
+          <t>6961594</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A04-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A04-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18424</t>
+          <t>16985</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13941</t>
+          <t>13156</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26674</t>
+          <t>26016</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>475640</t>
+          <t>477079</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>489997</t>
+          <t>490037</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>453548</t>
+          <t>454333</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>464412</t>
+          <t>464474</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>934879</t>
+          <t>935537</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>952127</t>
+          <t>951986</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14065</t>
+          <t>13873</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9738</t>
+          <t>9283</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25234</t>
+          <t>25961</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15584</t>
+          <t>14204</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34072</t>
+          <t>33379</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>721424</t>
+          <t>721616</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>732547</t>
+          <t>732583</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>600260</t>
+          <t>599533</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>615756</t>
+          <t>616211</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1326910</t>
+          <t>1327603</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1345398</t>
+          <t>1346778</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11126</t>
+          <t>11284</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>7280</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24223</t>
+          <t>22177</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>11707</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28930</t>
+          <t>29349</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>626523</t>
+          <t>626365</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>635777</t>
+          <t>635760</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>665521</t>
+          <t>667567</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>681904</t>
+          <t>682464</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1298464</t>
+          <t>1298045</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1316321</t>
+          <t>1315687</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16115</t>
+          <t>15981</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>14574</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>9043</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24308</t>
+          <t>25443</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>503032</t>
+          <t>503166</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>515364</t>
+          <t>515403</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>501761</t>
+          <t>501068</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>512596</t>
+          <t>512588</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1010481</t>
+          <t>1009346</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1026125</t>
+          <t>1025746</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>6830</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22150</t>
+          <t>21007</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16708</t>
+          <t>16815</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13944</t>
+          <t>13984</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32215</t>
+          <t>31743</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>364560</t>
+          <t>365703</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>379419</t>
+          <t>379880</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>387278</t>
+          <t>387171</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>399602</t>
+          <t>399568</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>758481</t>
+          <t>758953</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>776752</t>
+          <t>776712</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15640</t>
+          <t>15374</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>5412</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16616</t>
+          <t>17811</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28188</t>
+          <t>27855</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276943</t>
+          <t>277209</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>288016</t>
+          <t>287978</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>326318</t>
+          <t>325123</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>337508</t>
+          <t>337522</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>607329</t>
+          <t>607662</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>623490</t>
+          <t>624181</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15805</t>
+          <t>15641</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19527</t>
+          <t>19223</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11245</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29447</t>
+          <t>30693</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>194078</t>
+          <t>194242</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>206288</t>
+          <t>206070</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>314381</t>
+          <t>314685</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>328691</t>
+          <t>328946</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>514344</t>
+          <t>513098</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>532546</t>
+          <t>532370</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>45311</t>
+          <t>45808</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>75059</t>
+          <t>76703</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59272</t>
+          <t>57529</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>93543</t>
+          <t>93713</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>112191</t>
+          <t>112708</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>155307</t>
+          <t>159284</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3200466</t>
+          <t>3198822</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3230214</t>
+          <t>3229717</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3285654</t>
+          <t>3285484</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3319925</t>
+          <t>3321668</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6499415</t>
+          <t>6495438</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6542531</t>
+          <t>6542014</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16890</t>
+          <t>16406</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8992</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23934</t>
+          <t>24039</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16419</t>
+          <t>16360</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35965</t>
+          <t>35207</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>436215</t>
+          <t>436699</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>449134</t>
+          <t>449000</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>405405</t>
+          <t>405300</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>420347</t>
+          <t>420486</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>846480</t>
+          <t>847238</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>866026</t>
+          <t>866085</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12145</t>
+          <t>11404</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30842</t>
+          <t>29489</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17755</t>
+          <t>17983</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39821</t>
+          <t>40457</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33193</t>
+          <t>34206</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63245</t>
+          <t>63860</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>655396</t>
+          <t>656749</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>674093</t>
+          <t>674834</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>570434</t>
+          <t>569798</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>592500</t>
+          <t>592272</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1233248</t>
+          <t>1232633</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1263300</t>
+          <t>1262287</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>8995</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25210</t>
+          <t>25788</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10675</t>
+          <t>11058</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>28539</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22817</t>
+          <t>23860</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46457</t>
+          <t>47644</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>653950</t>
+          <t>653372</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>670451</t>
+          <t>670165</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>675097</t>
+          <t>676398</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>694262</t>
+          <t>693879</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1337640</t>
+          <t>1336453</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1361280</t>
+          <t>1360237</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21285</t>
+          <t>21752</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18828</t>
+          <t>18292</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13316</t>
+          <t>13705</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33243</t>
+          <t>33123</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>593332</t>
+          <t>592865</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>608321</t>
+          <t>609293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>595244</t>
+          <t>595780</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>608825</t>
+          <t>609551</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1195446</t>
+          <t>1195566</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1215373</t>
+          <t>1214984</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23010</t>
+          <t>23404</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16467</t>
+          <t>15964</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13541</t>
+          <t>13030</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33240</t>
+          <t>33679</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>405334</t>
+          <t>404940</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>421534</t>
+          <t>421750</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>431333</t>
+          <t>431836</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>443682</t>
+          <t>443674</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>842904</t>
+          <t>842465</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>862603</t>
+          <t>863114</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9386</t>
+          <t>9569</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31815</t>
+          <t>30096</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>4661</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17729</t>
+          <t>17387</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16640</t>
+          <t>17021</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41738</t>
+          <t>41893</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>275980</t>
+          <t>277699</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>298409</t>
+          <t>298226</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>335330</t>
+          <t>335672</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>348362</t>
+          <t>348398</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>619116</t>
+          <t>618961</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>644214</t>
+          <t>643833</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18125</t>
+          <t>19401</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6981</t>
+          <t>6658</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21517</t>
+          <t>21090</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14151</t>
+          <t>14266</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33846</t>
+          <t>36604</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>228719</t>
+          <t>227443</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>242375</t>
+          <t>242189</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>365236</t>
+          <t>365663</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>379772</t>
+          <t>380095</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>599751</t>
+          <t>596993</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>619446</t>
+          <t>619331</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>76700</t>
+          <t>77743</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>118937</t>
+          <t>121968</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>80717</t>
+          <t>83879</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>122792</t>
+          <t>124616</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>168871</t>
+          <t>168997</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>228183</t>
+          <t>230362</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3297166</t>
+          <t>3294135</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3339403</t>
+          <t>3338360</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3423425</t>
+          <t>3421601</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3465500</t>
+          <t>3462338</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6734137</t>
+          <t>6731958</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6793449</t>
+          <t>6793323</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7578</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17446</t>
+          <t>16863</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7511</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20512</t>
+          <t>21832</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411885</t>
+          <t>410091</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>378309</t>
+          <t>378892</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>390892</t>
+          <t>390874</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>794706</t>
+          <t>793386</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>807707</t>
+          <t>808278</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11841</t>
+          <t>11772</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28913</t>
+          <t>30012</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8227</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22672</t>
+          <t>24041</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23788</t>
+          <t>22138</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45447</t>
+          <t>45001</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>561583</t>
+          <t>560484</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>578655</t>
+          <t>578724</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>540872</t>
+          <t>539503</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>555201</t>
+          <t>555317</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1108593</t>
+          <t>1109039</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1130252</t>
+          <t>1131902</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25427</t>
+          <t>24501</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24514</t>
+          <t>24009</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19271</t>
+          <t>20026</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41038</t>
+          <t>41631</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>643670</t>
+          <t>644596</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>660112</t>
+          <t>660624</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>636872</t>
+          <t>637377</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>652897</t>
+          <t>653081</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1289445</t>
+          <t>1288852</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1311212</t>
+          <t>1310457</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>6142</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20660</t>
+          <t>20603</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11627</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10295</t>
+          <t>10135</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28305</t>
+          <t>27267</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>625388</t>
+          <t>625445</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>639762</t>
+          <t>639906</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>637438</t>
+          <t>637450</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>647837</t>
+          <t>647097</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1266820</t>
+          <t>1267858</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1284830</t>
+          <t>1284990</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18362</t>
+          <t>17821</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9860</t>
+          <t>10132</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27693</t>
+          <t>27461</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17605</t>
+          <t>17642</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39018</t>
+          <t>41062</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>459556</t>
+          <t>460097</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>473422</t>
+          <t>473282</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>469156</t>
+          <t>469388</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>486989</t>
+          <t>486717</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>935749</t>
+          <t>933705</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>957162</t>
+          <t>957125</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>16608</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18295</t>
+          <t>17593</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10087</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28743</t>
+          <t>29388</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>315871</t>
+          <t>317722</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>330453</t>
+          <t>330117</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>359467</t>
+          <t>360169</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>374003</t>
+          <t>374529</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>683349</t>
+          <t>682704</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>702005</t>
+          <t>701333</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19244</t>
+          <t>19252</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22671</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>251195</t>
+          <t>251990</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>380925</t>
+          <t>380917</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>395178</t>
+          <t>395222</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>634496</t>
+          <t>636458</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>650773</t>
+          <t>651344</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53214</t>
+          <t>54463</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>86710</t>
+          <t>88587</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>63836</t>
+          <t>63356</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>101231</t>
+          <t>101368</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>126017</t>
+          <t>126736</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>177249</t>
+          <t>179493</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3307640</t>
+          <t>3305763</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3341136</t>
+          <t>3339887</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3443311</t>
+          <t>3443174</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3480706</t>
+          <t>3481186</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6761643</t>
+          <t>6759399</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6812875</t>
+          <t>6812156</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7758</t>
+          <t>7274</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>1679</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21421</t>
+          <t>20459</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7211</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>19606</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14969</t>
+          <t>17177</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30805</t>
+          <t>32659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>392229</t>
+          <t>400519</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>378566</t>
+          <t>387334</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>397857</t>
+          <t>406114</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>305989</t>
+          <t>352609</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>295940</t>
+          <t>342906</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311028</t>
+          <t>358523</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>698218</t>
+          <t>753128</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>682382</t>
+          <t>737646</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>706758</t>
+          <t>761664</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15120</t>
+          <t>19222</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10979</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>7015</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>21642</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>14923</t>
+          <t>18819</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25992</t>
+          <t>30618</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>419603</t>
+          <t>470516</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>408427</t>
+          <t>457668</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423280</t>
+          <t>475513</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>500525</t>
+          <t>488639</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>491691</t>
+          <t>479441</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>506589</t>
+          <t>494068</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>920128</t>
+          <t>959154</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>909059</t>
+          <t>947355</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>927067</t>
+          <t>967861</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>13352</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22366</t>
+          <t>22536</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15222</t>
+          <t>17721</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9745</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22684</t>
+          <t>26220</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>28332</t>
+          <t>31073</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>21946</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39691</t>
+          <t>42045</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>523229</t>
+          <t>607485</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>513972</t>
+          <t>598301</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>529614</t>
+          <t>613680</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>527246</t>
+          <t>604418</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>519784</t>
+          <t>595919</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>532723</t>
+          <t>610676</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1050474</t>
+          <t>1211903</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1039115</t>
+          <t>1200931</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1058851</t>
+          <t>1221030</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18678</t>
+          <t>20792</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>12867</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31889</t>
+          <t>33859</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24573</t>
+          <t>21278</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15964</t>
+          <t>15258</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42614</t>
+          <t>29390</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>43252</t>
+          <t>42070</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26265</t>
+          <t>30403</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66641</t>
+          <t>56555</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>869108</t>
+          <t>679825</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>855897</t>
+          <t>666758</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>880477</t>
+          <t>687750</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>688308</t>
+          <t>715608</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>670267</t>
+          <t>707496</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>696917</t>
+          <t>721628</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1557415</t>
+          <t>1395434</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1534026</t>
+          <t>1380949</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1574402</t>
+          <t>1407101</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>13995</t>
+          <t>14948</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22023</t>
+          <t>23114</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>21065</t>
+          <t>26175</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>18910</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28268</t>
+          <t>33986</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>35059</t>
+          <t>41124</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26586</t>
+          <t>32234</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46388</t>
+          <t>53170</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>546242</t>
+          <t>593411</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>538214</t>
+          <t>585245</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>551831</t>
+          <t>599506</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>523822</t>
+          <t>581273</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>573462</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>529729</t>
+          <t>588538</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1070065</t>
+          <t>1174683</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1058736</t>
+          <t>1162637</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1078538</t>
+          <t>1183573</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9527</t>
+          <t>10280</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5429</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15763</t>
+          <t>16388</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13840</t>
+          <t>15408</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23421</t>
+          <t>21156</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>23367</t>
+          <t>25688</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11888</t>
+          <t>18586</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34269</t>
+          <t>34091</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>358638</t>
+          <t>396800</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>352402</t>
+          <t>390692</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>362970</t>
+          <t>401651</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>594528</t>
+          <t>423758</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>584947</t>
+          <t>418010</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>604512</t>
+          <t>428861</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>953166</t>
+          <t>820558</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>942264</t>
+          <t>812155</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>964645</t>
+          <t>827660</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>9128</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14215</t>
+          <t>16635</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>18766</t>
+          <t>21212</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13062</t>
+          <t>15317</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27245</t>
+          <t>31175</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>26949</t>
+          <t>30340</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19649</t>
+          <t>22355</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35554</t>
+          <t>40592</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>274086</t>
+          <t>300575</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>268054</t>
+          <t>293068</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>277479</t>
+          <t>304355</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>405628</t>
+          <t>441867</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>397149</t>
+          <t>431904</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>411332</t>
+          <t>447762</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>679714</t>
+          <t>742442</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>671109</t>
+          <t>732190</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>687014</t>
+          <t>750427</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282269</t>
+          <t>309703</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282269</t>
+          <t>309703</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282269</t>
+          <t>309703</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>706663</t>
+          <t>772782</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>706663</t>
+          <t>772782</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>706663</t>
+          <t>772782</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>75194</t>
+          <t>82148</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54005</t>
+          <t>64087</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>97118</t>
+          <t>104513</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>111657</t>
+          <t>124142</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>91030</t>
+          <t>105311</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>136067</t>
+          <t>144065</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>186852</t>
+          <t>206290</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>154438</t>
+          <t>182214</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>216564</t>
+          <t>236764</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3383136</t>
+          <t>3449132</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3361212</t>
+          <t>3426767</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3404325</t>
+          <t>3467193</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3546045</t>
+          <t>3608171</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3521635</t>
+          <t>3588248</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3566672</t>
+          <t>3627002</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6929180</t>
+          <t>7057303</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6899468</t>
+          <t>7026829</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6961594</t>
+          <t>7081379</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
